--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="134">
   <si>
     <t>Materia</t>
   </si>
@@ -3425,28 +3425,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3454,27 +3469,72 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -3482,22 +3542,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>88.90000000000001</v>
       </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>88.90000000000001</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3505,22 +3610,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C5">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>95</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>88.90000000000001</v>
       </c>
-      <c r="G5">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>95</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>95</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3528,22 +3678,67 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>90</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>90</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3551,22 +3746,67 @@
         <v>77.8</v>
       </c>
       <c r="C7">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>95</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>77.8</v>
       </c>
-      <c r="G7">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>77.8</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>95</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -3574,22 +3814,67 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>94.40000000000001</v>
       </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>94.40000000000001</v>
       </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -3597,22 +3882,67 @@
         <v>83.3</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>83.3</v>
       </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>83.3</v>
       </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -3620,22 +3950,67 @@
         <v>77.8</v>
       </c>
       <c r="C10">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>80</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>77.8</v>
       </c>
-      <c r="G10">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>77.8</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>80</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -3643,22 +4018,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>88.90000000000001</v>
       </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>88.90000000000001</v>
       </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -3666,22 +4086,67 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>100</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -3689,22 +4154,67 @@
         <v>83.3</v>
       </c>
       <c r="C13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>90</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>83.3</v>
       </c>
-      <c r="G13">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>83.3</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>90</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -3712,22 +4222,67 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -3735,22 +4290,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>88.90000000000001</v>
       </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-      <c r="F15">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>88.90000000000001</v>
       </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -3758,22 +4358,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>88.90000000000001</v>
       </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-      <c r="F16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
         <v>88.90000000000001</v>
       </c>
-      <c r="G16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -3781,22 +4426,67 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>100</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -3804,22 +4494,67 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>94.40000000000001</v>
       </c>
-      <c r="E18">
-        <v>100</v>
-      </c>
-      <c r="F18">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
         <v>94.40000000000001</v>
       </c>
-      <c r="G18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -3827,22 +4562,67 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>94.40000000000001</v>
       </c>
-      <c r="E19">
-        <v>100</v>
-      </c>
-      <c r="F19">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>94.40000000000001</v>
       </c>
-      <c r="G19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -3850,22 +4630,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>88.90000000000001</v>
       </c>
-      <c r="E20">
-        <v>100</v>
-      </c>
-      <c r="F20">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>88.90000000000001</v>
       </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -3873,22 +4698,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C21">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>95</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>88.90000000000001</v>
       </c>
-      <c r="G21">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>95</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -3896,22 +4766,67 @@
         <v>83.3</v>
       </c>
       <c r="C22">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>95</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>83.3</v>
       </c>
-      <c r="G22">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>95</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>83.3</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>95</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -3919,22 +4834,67 @@
         <v>83.3</v>
       </c>
       <c r="C23">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>95</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>83.3</v>
       </c>
-      <c r="G23">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>83.3</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>95</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -3942,22 +4902,67 @@
         <v>83.3</v>
       </c>
       <c r="C24">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>95</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>83.3</v>
       </c>
-      <c r="G24">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>95</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>83.3</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>95</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -3965,22 +4970,67 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -3988,22 +5038,67 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>100</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -4011,22 +5106,67 @@
         <v>77.8</v>
       </c>
       <c r="C27">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>77.8</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>95</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>77.8</v>
       </c>
-      <c r="G27">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>95</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>77.8</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>95</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
@@ -4034,22 +5174,67 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -4057,22 +5242,67 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <v>94.40000000000001</v>
       </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
-      <c r="F29">
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>94.40000000000001</v>
       </c>
-      <c r="G29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -4080,22 +5310,67 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C30">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>90</v>
       </c>
       <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>88.90000000000001</v>
       </c>
-      <c r="G30">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>90</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,26 +5378,71 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Miguel Lopez Yadira</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Miguel Lopez Yadira</t>
-  </si>
-  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
@@ -206,220 +206,70 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>NAZARIO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
     <t>ATENOGENES</t>
   </si>
   <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
     <t>DULIAM</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
     <t>ARIEL</t>
   </si>
   <si>
     <t>EDGAR</t>
   </si>
   <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
     <t>ISAAC</t>
   </si>
   <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -928,7 +778,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -940,7 +790,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -952,19 +802,19 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -991,10 +841,10 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -1003,10 +853,10 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1017,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -1029,7 +879,7 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1041,19 +891,19 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1080,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1092,7 +942,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1106,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1118,7 +968,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -1130,19 +980,19 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1169,22 +1019,22 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1195,7 +1045,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1207,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -1219,19 +1069,19 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1258,10 +1108,10 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1270,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1284,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1296,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>8</v>
@@ -1308,19 +1158,19 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1347,10 +1197,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1359,7 +1209,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1373,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1385,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -1397,19 +1247,19 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1436,10 +1286,10 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1448,10 +1298,10 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1462,7 +1312,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1474,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1486,19 +1336,19 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1525,7 +1375,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1537,7 +1387,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1551,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -1563,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>8</v>
@@ -1575,19 +1425,19 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1614,10 +1464,10 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -1626,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1640,7 +1490,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1652,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -1664,19 +1514,19 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1703,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1715,7 +1565,7 @@
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -1729,7 +1579,7 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1741,7 +1591,7 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -1753,19 +1603,19 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1792,7 +1642,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1804,10 +1654,10 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1818,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -1830,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H14">
         <v>9</v>
@@ -1842,19 +1692,19 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1881,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1890,13 +1740,13 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1907,7 +1757,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1919,7 +1769,7 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -1931,19 +1781,19 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1970,7 +1820,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1979,13 +1829,13 @@
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1996,7 +1846,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -2008,7 +1858,7 @@
         <v>9</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H16">
         <v>7</v>
@@ -2020,19 +1870,19 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2059,22 +1909,22 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2085,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -2097,7 +1947,7 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H17">
         <v>9</v>
@@ -2109,19 +1959,19 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2148,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2157,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2174,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2186,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>8</v>
@@ -2198,19 +2048,19 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2237,7 +2087,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2246,13 +2096,13 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2263,7 +2113,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2275,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>9</v>
@@ -2287,19 +2137,19 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2326,10 +2176,10 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2338,10 +2188,10 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2352,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2364,7 +2214,7 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>8</v>
@@ -2376,19 +2226,19 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2415,10 +2265,10 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2427,10 +2277,10 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2441,7 +2291,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2453,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>8</v>
@@ -2465,19 +2315,19 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2504,10 +2354,10 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>10</v>
@@ -2516,7 +2366,7 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2530,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2542,7 +2392,7 @@
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>8</v>
@@ -2554,19 +2404,19 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2593,10 +2443,10 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>6</v>
@@ -2605,10 +2455,10 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2619,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -2631,7 +2481,7 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>8</v>
@@ -2643,19 +2493,19 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2682,10 +2532,10 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2694,10 +2544,10 @@
         <v>6</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2708,7 +2558,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2720,7 +2570,7 @@
         <v>7</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H24">
         <v>7</v>
@@ -2732,19 +2582,19 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2771,22 +2621,22 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2797,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2809,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>9</v>
@@ -2821,19 +2671,19 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2860,10 +2710,10 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2872,7 +2722,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -2886,7 +2736,7 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -2898,7 +2748,7 @@
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H26">
         <v>8</v>
@@ -2910,19 +2760,19 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2949,22 +2799,22 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2975,7 +2825,7 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2987,7 +2837,7 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>7</v>
@@ -2999,19 +2849,19 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3038,22 +2888,22 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3064,7 +2914,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -3076,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -3088,19 +2938,19 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3127,19 +2977,19 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3153,7 +3003,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -3165,7 +3015,7 @@
         <v>9</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>9</v>
@@ -3177,19 +3027,19 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3216,10 +3066,10 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3228,7 +3078,7 @@
         <v>9</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3242,7 +3092,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -3254,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H30">
         <v>8</v>
@@ -3266,19 +3116,19 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3305,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3314,10 +3164,10 @@
         <v>6</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3331,7 +3181,7 @@
         <v>9</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3343,7 +3193,7 @@
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>9</v>
@@ -3355,19 +3205,19 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3394,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3406,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3542,64 +3392,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I4">
         <v>88.90000000000001</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P4">
         <v>88.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3610,64 +3460,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="E5">
         <v>95</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>73.7</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>88.90000000000001</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>76.3</v>
       </c>
       <c r="L5">
         <v>95</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="P5">
         <v>88.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>76.3</v>
       </c>
       <c r="S5">
         <v>95</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3678,64 +3528,64 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="E6">
         <v>90</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L6">
         <v>90</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S6">
         <v>90</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3746,64 +3596,64 @@
         <v>77.8</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>95</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>77.8</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L7">
         <v>95</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="P7">
         <v>77.8</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="S7">
         <v>95</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3814,64 +3664,64 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I8">
         <v>94.40000000000001</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P8">
         <v>94.40000000000001</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3882,64 +3732,64 @@
         <v>83.3</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I9">
         <v>83.3</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>83.3</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3950,64 +3800,64 @@
         <v>77.8</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>80</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I10">
         <v>77.8</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L10">
         <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="P10">
         <v>77.8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="S10">
         <v>80</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4018,64 +3868,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>88.90000000000001</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P11">
         <v>88.90000000000001</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4086,64 +3936,64 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4154,64 +4004,64 @@
         <v>83.3</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>90</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I13">
         <v>83.3</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="L13">
         <v>90</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="P13">
         <v>83.3</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="S13">
         <v>90</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4222,64 +4072,64 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4290,64 +4140,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I15">
         <v>88.90000000000001</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P15">
         <v>88.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4358,64 +4208,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I16">
         <v>88.90000000000001</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P16">
         <v>88.90000000000001</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4426,64 +4276,64 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4494,64 +4344,64 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I18">
         <v>94.40000000000001</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
         <v>94.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4562,64 +4412,64 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I19">
         <v>94.40000000000001</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P19">
         <v>94.40000000000001</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4630,64 +4480,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I20">
         <v>88.90000000000001</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P20">
         <v>88.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4698,64 +4548,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>95</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I21">
         <v>88.90000000000001</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L21">
         <v>95</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P21">
         <v>88.90000000000001</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S21">
         <v>95</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4766,64 +4616,64 @@
         <v>83.3</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>95</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I22">
         <v>83.3</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="L22">
         <v>95</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="P22">
         <v>83.3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="S22">
         <v>95</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4834,64 +4684,64 @@
         <v>83.3</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>95</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>83.3</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L23">
         <v>95</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="P23">
         <v>83.3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="S23">
         <v>95</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4902,64 +4752,64 @@
         <v>83.3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>95</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I24">
         <v>83.3</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>95</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P24">
         <v>83.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
         <v>95</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4970,64 +4820,64 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5038,64 +4888,64 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="P26">
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5106,64 +4956,64 @@
         <v>77.8</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>95</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I27">
         <v>77.8</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L27">
         <v>95</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P27">
         <v>77.8</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S27">
         <v>95</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5174,64 +5024,64 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I28">
         <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5242,64 +5092,64 @@
         <v>94.40000000000001</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I29">
         <v>94.40000000000001</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>94.40000000000001</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5310,64 +5160,64 @@
         <v>88.90000000000001</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>90</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I30">
         <v>88.90000000000001</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L30">
         <v>90</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="P30">
         <v>88.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S30">
         <v>90</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5378,64 +5228,64 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5492,7 +5342,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5501,27 +5351,30 @@
         <v>28</v>
       </c>
       <c r="D2">
+        <v>22</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>21.4</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5530,27 +5383,30 @@
         <v>28</v>
       </c>
       <c r="D3">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G3" s="2">
+        <v>17.9</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>28</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -5559,19 +5415,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>78.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G4" s="2">
-        <v>21.4</v>
+        <v>10.7</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5582,7 +5438,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5591,19 +5447,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>82.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G5" s="2">
-        <v>17.9</v>
+        <v>10.7</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5617,22 +5473,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -5649,25 +5505,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5715,7 +5571,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5742,1126 +5598,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920005</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920005</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920008</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920008</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920049</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920049</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920010</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920355</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920355</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920078</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920078</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920011</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920011</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920195</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920195</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920160</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920160</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920012</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920012</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920018</v>
-      </c>
-      <c r="B24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920018</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920013</v>
-      </c>
-      <c r="B26" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920013</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920391</v>
-      </c>
-      <c r="B28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920391</v>
-      </c>
-      <c r="B29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920015</v>
-      </c>
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920015</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920016</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920016</v>
-      </c>
-      <c r="B33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920022</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920022</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920379</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920379</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920366</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920366</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920367</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920018</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920018</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920019</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920019</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920021</v>
-      </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920021</v>
-      </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920022</v>
-      </c>
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920022</v>
-      </c>
-      <c r="B49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920023</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920023</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920025</v>
-      </c>
-      <c r="B52" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" t="s">
-        <v>132</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920025</v>
-      </c>
-      <c r="B53" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" t="s">
-        <v>132</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920027</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>119</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920027</v>
-      </c>
-      <c r="B55" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920028</v>
-      </c>
-      <c r="B56" t="s">
-        <v>86</v>
-      </c>
-      <c r="C56" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" t="s">
-        <v>133</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920028</v>
-      </c>
-      <c r="B57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>54</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6869,7 +5605,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6901,922 +5637,255 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>20330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920003</v>
+        <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920010</v>
+        <v>21330051920023</v>
       </c>
       <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
         <v>66</v>
       </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920010</v>
+        <v>21330051920023</v>
       </c>
       <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
         <v>66</v>
       </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920011</v>
+        <v>21330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920011</v>
+        <v>20330051920049</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920160</v>
+        <v>20330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920160</v>
+        <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920012</v>
+        <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920012</v>
+        <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920018</v>
+        <v>21330051920022</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>54</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920013</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920391</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920391</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920015</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920015</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920016</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920016</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920022</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920022</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920379</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920379</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920366</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920366</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920367</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920367</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920018</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920018</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920019</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920019</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>128</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920021</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920021</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920025</v>
-      </c>
-      <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920025</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920027</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920027</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920028</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920028</v>
-      </c>
-      <c r="B41" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -206,6 +206,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -215,34 +218,25 @@
     <t>BAEZ</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>NAZARIO</t>
   </si>
   <si>
-    <t>ATENOGENES</t>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -254,22 +248,16 @@
     <t>LUIS EDUARDO</t>
   </si>
   <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
     <t>DULIAM</t>
   </si>
   <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
     <t>EDGAR</t>
   </si>
   <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
     <t>ISAAC</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
   </si>
 </sst>
 </file>
@@ -796,16 +784,16 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -885,16 +873,16 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -936,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>5</v>
@@ -974,16 +962,16 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1016,10 +1004,10 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1063,16 +1051,16 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1105,10 +1093,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1152,16 +1140,16 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1241,16 +1229,16 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1286,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1330,16 +1318,16 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1375,7 +1363,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1419,16 +1407,16 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1461,16 +1449,16 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>8</v>
@@ -1508,16 +1496,16 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -1597,16 +1585,16 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1642,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1686,16 +1674,16 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1728,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1737,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1775,16 +1763,16 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1817,16 +1805,16 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1864,16 +1852,16 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1906,16 +1894,16 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -1953,16 +1941,16 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -2004,7 +1992,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2042,16 +2030,16 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2084,16 +2072,16 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2131,16 +2119,16 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2176,13 +2164,13 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2220,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -2265,13 +2253,13 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA20">
         <v>9</v>
@@ -2309,16 +2297,16 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2360,7 +2348,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2398,16 +2386,16 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2440,10 +2428,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2487,16 +2475,16 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2532,7 +2520,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2576,16 +2564,16 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2665,16 +2653,16 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2716,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -2754,16 +2742,16 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -2796,16 +2784,16 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -2843,16 +2831,16 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>7</v>
@@ -2885,7 +2873,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2894,7 +2882,7 @@
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -2932,16 +2920,16 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2983,7 +2971,7 @@
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>8</v>
@@ -3021,16 +3009,16 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -3072,7 +3060,7 @@
         <v>7</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -3110,16 +3098,16 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -3155,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3199,16 +3187,16 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3250,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3410,7 +3398,7 @@
         <v>90</v>
       </c>
       <c r="I4">
-        <v>88.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3431,7 +3419,7 @@
         <v>94.7</v>
       </c>
       <c r="P4">
-        <v>88.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3478,7 +3466,7 @@
         <v>80</v>
       </c>
       <c r="I5">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3487,7 +3475,7 @@
         <v>76.3</v>
       </c>
       <c r="L5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
         <v>75.7</v>
@@ -3499,7 +3487,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="P5">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3508,7 +3496,7 @@
         <v>76.3</v>
       </c>
       <c r="S5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T5">
         <v>75.7</v>
@@ -3555,7 +3543,7 @@
         <v>94.7</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M6">
         <v>97.3</v>
@@ -3576,7 +3564,7 @@
         <v>94.7</v>
       </c>
       <c r="S6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T6">
         <v>97.3</v>
@@ -3614,7 +3602,7 @@
         <v>90</v>
       </c>
       <c r="I7">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3623,7 +3611,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="L7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M7">
         <v>91.90000000000001</v>
@@ -3635,7 +3623,7 @@
         <v>89.5</v>
       </c>
       <c r="P7">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3644,7 +3632,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="S7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T7">
         <v>91.90000000000001</v>
@@ -3682,7 +3670,7 @@
         <v>95</v>
       </c>
       <c r="I8">
-        <v>94.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3703,7 +3691,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P8">
-        <v>94.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3750,7 +3738,7 @@
         <v>95</v>
       </c>
       <c r="I9">
-        <v>83.3</v>
+        <v>91.2</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3771,7 +3759,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>83.3</v>
+        <v>91.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3818,16 +3806,16 @@
         <v>90</v>
       </c>
       <c r="I10">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K10">
         <v>71.09999999999999</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M10">
         <v>59.5</v>
@@ -3839,16 +3827,16 @@
         <v>63.2</v>
       </c>
       <c r="P10">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R10">
         <v>71.09999999999999</v>
       </c>
       <c r="S10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T10">
         <v>59.5</v>
@@ -3886,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3907,7 +3895,7 @@
         <v>94.7</v>
       </c>
       <c r="P11">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3954,7 +3942,7 @@
         <v>95</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3975,7 +3963,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4022,16 +4010,16 @@
         <v>85</v>
       </c>
       <c r="I13">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K13">
         <v>89.5</v>
       </c>
       <c r="L13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M13">
         <v>94.59999999999999</v>
@@ -4043,16 +4031,16 @@
         <v>86.8</v>
       </c>
       <c r="P13">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R13">
         <v>89.5</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T13">
         <v>94.59999999999999</v>
@@ -4093,7 +4081,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K14">
         <v>92.09999999999999</v>
@@ -4114,7 +4102,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="R14">
         <v>92.09999999999999</v>
@@ -4158,10 +4146,10 @@
         <v>90</v>
       </c>
       <c r="I15">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K15">
         <v>89.5</v>
@@ -4179,10 +4167,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="P15">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R15">
         <v>89.5</v>
@@ -4226,7 +4214,7 @@
         <v>95</v>
       </c>
       <c r="I16">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -4247,7 +4235,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P16">
-        <v>88.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4362,7 +4350,7 @@
         <v>95</v>
       </c>
       <c r="I18">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4383,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4430,10 +4418,10 @@
         <v>85</v>
       </c>
       <c r="I19">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4451,10 +4439,10 @@
         <v>94.7</v>
       </c>
       <c r="P19">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4498,7 +4486,7 @@
         <v>85</v>
       </c>
       <c r="I20">
-        <v>88.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4519,7 +4507,7 @@
         <v>94.7</v>
       </c>
       <c r="P20">
-        <v>88.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4566,7 +4554,7 @@
         <v>95</v>
       </c>
       <c r="I21">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4575,7 +4563,7 @@
         <v>94.7</v>
       </c>
       <c r="L21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M21">
         <v>97.3</v>
@@ -4587,7 +4575,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="P21">
-        <v>88.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4596,7 +4584,7 @@
         <v>94.7</v>
       </c>
       <c r="S21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T21">
         <v>97.3</v>
@@ -4634,16 +4622,16 @@
         <v>85</v>
       </c>
       <c r="I22">
-        <v>83.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K22">
         <v>92.09999999999999</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M22">
         <v>91.90000000000001</v>
@@ -4655,16 +4643,16 @@
         <v>86.8</v>
       </c>
       <c r="P22">
-        <v>83.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R22">
         <v>92.09999999999999</v>
       </c>
       <c r="S22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T22">
         <v>91.90000000000001</v>
@@ -4702,16 +4690,16 @@
         <v>90</v>
       </c>
       <c r="I23">
-        <v>83.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K23">
         <v>81.59999999999999</v>
       </c>
       <c r="L23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M23">
         <v>86.5</v>
@@ -4723,16 +4711,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="P23">
-        <v>83.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R23">
         <v>81.59999999999999</v>
       </c>
       <c r="S23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T23">
         <v>86.5</v>
@@ -4770,7 +4758,7 @@
         <v>90</v>
       </c>
       <c r="I24">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4779,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M24">
         <v>97.3</v>
@@ -4791,7 +4779,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P24">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4800,7 +4788,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T24">
         <v>97.3</v>
@@ -4906,10 +4894,10 @@
         <v>90</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K26">
         <v>89.5</v>
@@ -4927,10 +4915,10 @@
         <v>86.8</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R26">
         <v>89.5</v>
@@ -4974,7 +4962,7 @@
         <v>90</v>
       </c>
       <c r="I27">
-        <v>77.8</v>
+        <v>88.2</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4983,7 +4971,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="L27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M27">
         <v>94.59999999999999</v>
@@ -4995,7 +4983,7 @@
         <v>94.7</v>
       </c>
       <c r="P27">
-        <v>77.8</v>
+        <v>88.2</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5004,7 +4992,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T27">
         <v>94.59999999999999</v>
@@ -5042,7 +5030,7 @@
         <v>95</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -5063,7 +5051,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5110,7 +5098,7 @@
         <v>95</v>
       </c>
       <c r="I29">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5131,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5178,7 +5166,7 @@
         <v>95</v>
       </c>
       <c r="I30">
-        <v>88.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5187,7 +5175,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="L30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5199,7 +5187,7 @@
         <v>94.7</v>
       </c>
       <c r="P30">
-        <v>88.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5208,7 +5196,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5395,7 +5383,7 @@
         <v>17.9</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5459,7 +5447,7 @@
         <v>10.7</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5555,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5637,22 +5625,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5660,22 +5648,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5683,7 +5671,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920023</v>
+        <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -5692,13 +5680,13 @@
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5706,7 +5694,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920023</v>
+        <v>20330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5715,7 +5703,7 @@
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5729,22 +5717,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920003</v>
+        <v>21330051920023</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5752,22 +5740,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920049</v>
+        <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5775,22 +5763,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920078</v>
+        <v>21330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5798,19 +5786,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920012</v>
+        <v>20330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -5824,13 +5812,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5844,22 +5832,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920367</v>
+        <v>21330051920015</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5867,22 +5855,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920022</v>
+        <v>20330051920367</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
@@ -209,24 +209,21 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -239,22 +236,19 @@
     <t>ARIEL</t>
   </si>
   <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
     <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
   </si>
   <si>
     <t>ISAAC</t>
@@ -820,7 +814,7 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -841,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -894,7 +888,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -909,13 +903,13 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -983,7 +977,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -998,7 +992,7 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1019,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1087,7 +1081,7 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1176,7 +1170,7 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1197,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1250,7 +1244,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1265,13 +1259,13 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1286,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>7</v>
@@ -1354,7 +1348,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1428,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1443,13 +1437,13 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1517,7 +1511,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1532,7 +1526,7 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1621,7 +1615,7 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1642,7 +1636,7 @@
         <v>5</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1710,7 +1704,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1731,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1799,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1888,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1962,7 +1956,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1977,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2066,7 +2060,7 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2140,7 +2134,7 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2155,13 +2149,13 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2229,7 +2223,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2244,13 +2238,13 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2318,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2333,13 +2327,13 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2422,7 +2416,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2443,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2511,7 +2505,7 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2585,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2600,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2689,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2710,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -2778,7 +2772,7 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2799,7 +2793,7 @@
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -2852,7 +2846,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2867,13 +2861,13 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2888,7 +2882,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -2941,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2956,13 +2950,13 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2977,7 +2971,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3030,7 +3024,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3045,7 +3039,7 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3066,7 +3060,7 @@
         <v>9</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3134,7 +3128,7 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3155,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3208,7 +3202,7 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3223,7 +3217,7 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3244,7 +3238,7 @@
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -5371,19 +5365,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5394,7 +5388,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -5415,7 +5409,7 @@
         <v>10.7</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5426,10 +5420,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>28</v>
@@ -5447,7 +5441,7 @@
         <v>10.7</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5458,7 +5452,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -5490,28 +5484,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>28</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5593,7 +5587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5631,10 +5625,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5654,10 +5648,10 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -5671,22 +5665,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920366</v>
+        <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5694,22 +5688,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920366</v>
+        <v>20330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
         <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5717,22 +5711,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920023</v>
+        <v>20330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5740,22 +5734,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920023</v>
+        <v>21330051920015</v>
       </c>
       <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5763,22 +5757,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920003</v>
+        <v>20330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5786,16 +5780,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920078</v>
+        <v>20330051920367</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5804,75 +5798,6 @@
         <v>53</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920015</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920367</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,52 +206,37 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -799,16 +784,16 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -820,16 +805,16 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -891,13 +876,13 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -912,13 +897,13 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>5</v>
@@ -980,13 +965,13 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1066,16 +1051,16 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1087,7 +1072,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1155,16 +1140,16 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1179,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1247,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1274,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1333,16 +1318,16 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1357,13 +1342,13 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1425,13 +1410,13 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1514,13 +1499,13 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1600,16 +1585,16 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1689,16 +1674,16 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1778,16 +1763,16 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1799,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1808,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>7</v>
@@ -1867,16 +1852,16 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1897,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -1959,13 +1944,13 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2045,16 +2030,16 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2066,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2075,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2137,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2158,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2226,13 +2211,13 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2315,13 +2300,13 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2342,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2401,16 +2386,16 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2422,7 +2407,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2490,16 +2475,16 @@
         <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2511,10 +2496,10 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2582,13 +2567,13 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2603,7 +2588,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2668,16 +2653,16 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2689,7 +2674,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2757,16 +2742,16 @@
         <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2781,13 +2766,13 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -2849,13 +2834,13 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -2870,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2938,13 +2923,13 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3027,13 +3012,13 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3113,16 +3098,16 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3134,10 +3119,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3205,13 +3190,13 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3226,13 +3211,13 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3413,16 +3398,16 @@
         <v>94.7</v>
       </c>
       <c r="P4">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T4">
         <v>94.59999999999999</v>
@@ -3481,16 +3466,16 @@
         <v>71.09999999999999</v>
       </c>
       <c r="P5">
-        <v>85.3</v>
+        <v>90.7</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R5">
         <v>76.3</v>
       </c>
       <c r="S5">
-        <v>97.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T5">
         <v>75.7</v>
@@ -3558,7 +3543,7 @@
         <v>94.7</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="T6">
         <v>97.3</v>
@@ -3617,7 +3602,7 @@
         <v>89.5</v>
       </c>
       <c r="P7">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3626,7 +3611,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="S7">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="T7">
         <v>91.90000000000001</v>
@@ -3685,7 +3670,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P8">
-        <v>94.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3694,7 +3679,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T8">
         <v>91.90000000000001</v>
@@ -3753,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>91.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3762,7 +3747,7 @@
         <v>94.7</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T9">
         <v>97.3</v>
@@ -3821,16 +3806,16 @@
         <v>63.2</v>
       </c>
       <c r="P10">
-        <v>79.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="Q10">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="R10">
         <v>71.09999999999999</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="T10">
         <v>59.5</v>
@@ -3889,7 +3874,7 @@
         <v>94.7</v>
       </c>
       <c r="P11">
-        <v>88.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3957,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3966,7 +3951,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4025,16 +4010,16 @@
         <v>86.8</v>
       </c>
       <c r="P13">
-        <v>85.3</v>
+        <v>90.7</v>
       </c>
       <c r="Q13">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R13">
         <v>89.5</v>
       </c>
       <c r="S13">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T13">
         <v>94.59999999999999</v>
@@ -4093,10 +4078,10 @@
         <v>94.7</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q14">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R14">
         <v>92.09999999999999</v>
@@ -4161,16 +4146,16 @@
         <v>92.09999999999999</v>
       </c>
       <c r="P15">
-        <v>85.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R15">
         <v>89.5</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T15">
         <v>97.3</v>
@@ -4229,7 +4214,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P16">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4238,7 +4223,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4365,7 +4350,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4374,7 +4359,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4433,10 +4418,10 @@
         <v>94.7</v>
       </c>
       <c r="P19">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q19">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4501,7 +4486,7 @@
         <v>94.7</v>
       </c>
       <c r="P20">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4510,7 +4495,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4569,7 +4554,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="P21">
-        <v>88.2</v>
+        <v>90.7</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4578,7 +4563,7 @@
         <v>94.7</v>
       </c>
       <c r="S21">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="T21">
         <v>97.3</v>
@@ -4637,16 +4622,16 @@
         <v>86.8</v>
       </c>
       <c r="P22">
-        <v>82.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Q22">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R22">
         <v>92.09999999999999</v>
       </c>
       <c r="S22">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="T22">
         <v>91.90000000000001</v>
@@ -4705,16 +4690,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="P23">
-        <v>82.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R23">
         <v>81.59999999999999</v>
       </c>
       <c r="S23">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="T23">
         <v>86.5</v>
@@ -4773,7 +4758,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P24">
-        <v>88.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4782,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T24">
         <v>97.3</v>
@@ -4909,16 +4894,16 @@
         <v>86.8</v>
       </c>
       <c r="P26">
-        <v>91.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q26">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="R26">
         <v>89.5</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T26">
         <v>89.2</v>
@@ -4977,7 +4962,7 @@
         <v>94.7</v>
       </c>
       <c r="P27">
-        <v>88.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4986,7 +4971,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="S27">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T27">
         <v>94.59999999999999</v>
@@ -5045,7 +5030,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P28">
-        <v>91.2</v>
+        <v>90.7</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5054,7 +5039,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T28">
         <v>97.3</v>
@@ -5113,7 +5098,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5122,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5181,16 +5166,16 @@
         <v>94.7</v>
       </c>
       <c r="P30">
-        <v>94.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R30">
         <v>97.40000000000001</v>
       </c>
       <c r="S30">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5365,16 +5350,16 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -5388,10 +5373,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>28</v>
@@ -5409,7 +5394,7 @@
         <v>10.7</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5420,7 +5405,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -5452,28 +5437,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5484,7 +5469,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -5505,7 +5490,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5516,7 +5501,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -5537,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5587,7 +5572,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5619,16 +5604,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5642,19 +5627,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920012</v>
+        <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" t="s">
-        <v>71</v>
-      </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
@@ -5665,22 +5650,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920003</v>
+        <v>20330051920367</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5688,16 +5673,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920078</v>
+        <v>20330051920367</v>
       </c>
       <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
         <v>64</v>
       </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5711,22 +5696,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920018</v>
+        <v>20330051920049</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5734,22 +5719,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920015</v>
+        <v>20330051920078</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5757,47 +5742,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
         <v>67</v>
       </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920367</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -179,12 +179,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Miguel Lopez Yadira</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Miguel Lopez Yadira</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -215,13 +215,10 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -233,10 +230,7 @@
     <t>RAFAEL</t>
   </si>
   <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
+    <t>LUIS ENRIQUE</t>
   </si>
 </sst>
 </file>
@@ -790,19 +784,19 @@
         <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -879,19 +873,19 @@
         <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -968,19 +962,19 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -989,19 +983,19 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1057,19 +1051,19 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1078,13 +1072,13 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>6</v>
@@ -1146,19 +1140,19 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1167,7 +1161,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1235,19 +1229,19 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>6</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1262,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1324,19 +1318,19 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1413,19 +1407,19 @@
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1502,19 +1496,19 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1523,7 +1517,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1535,7 +1529,7 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1591,19 +1585,19 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1612,19 +1606,19 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1680,19 +1674,19 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1707,13 +1701,13 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1769,19 +1763,19 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>6</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1796,13 +1790,13 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1858,19 +1852,19 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1885,7 +1879,7 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -1947,19 +1941,19 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1974,13 +1968,13 @@
         <v>9</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2036,19 +2030,19 @@
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2063,13 +2057,13 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2125,19 +2119,19 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2214,19 +2208,19 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2247,7 +2241,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2303,19 +2297,19 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2392,19 +2386,19 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2481,19 +2475,19 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2508,13 +2502,13 @@
         <v>6</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2570,19 +2564,19 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2659,19 +2653,19 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2748,19 +2742,19 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>6</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2781,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2837,19 +2831,19 @@
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2864,13 +2858,13 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>8</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2926,19 +2920,19 @@
         <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -3015,19 +3009,19 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3036,7 +3030,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>8</v>
@@ -3104,19 +3098,19 @@
         <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3125,7 +3119,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3193,19 +3187,19 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3404,19 +3398,19 @@
         <v>93.8</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S4">
         <v>96.90000000000001</v>
       </c>
       <c r="T4">
-        <v>94.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3472,19 +3466,19 @@
         <v>93.8</v>
       </c>
       <c r="R5">
-        <v>76.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="S5">
         <v>89.09999999999999</v>
       </c>
       <c r="T5">
-        <v>75.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>71.09999999999999</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3540,19 +3534,19 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S6">
         <v>93.8</v>
       </c>
       <c r="T6">
-        <v>97.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3608,19 +3602,19 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="S7">
         <v>95.3</v>
       </c>
       <c r="T7">
-        <v>91.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="U7">
         <v>100</v>
       </c>
       <c r="V7">
-        <v>89.5</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3676,19 +3670,19 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="S8">
         <v>96.90000000000001</v>
       </c>
       <c r="T8">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="U8">
         <v>100</v>
       </c>
       <c r="V8">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3744,13 +3738,13 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S9">
         <v>96.90000000000001</v>
       </c>
       <c r="T9">
-        <v>97.3</v>
+        <v>98.3</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3812,19 +3806,19 @@
         <v>88.8</v>
       </c>
       <c r="R10">
-        <v>71.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="S10">
         <v>64.09999999999999</v>
       </c>
       <c r="T10">
-        <v>59.5</v>
+        <v>54.2</v>
       </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
-        <v>63.2</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3880,19 +3874,19 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>97.3</v>
+        <v>98.3</v>
       </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3948,19 +3942,19 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S12">
         <v>96.90000000000001</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U12">
         <v>100</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4016,19 +4010,19 @@
         <v>95</v>
       </c>
       <c r="R13">
-        <v>89.5</v>
+        <v>93.2</v>
       </c>
       <c r="S13">
         <v>90.59999999999999</v>
       </c>
       <c r="T13">
-        <v>94.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>86.8</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4084,19 +4078,19 @@
         <v>96.3</v>
       </c>
       <c r="R14">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="S14">
         <v>100</v>
       </c>
       <c r="T14">
-        <v>97.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4152,19 +4146,19 @@
         <v>97.5</v>
       </c>
       <c r="R15">
-        <v>89.5</v>
+        <v>91.5</v>
       </c>
       <c r="S15">
         <v>96.90000000000001</v>
       </c>
       <c r="T15">
-        <v>97.3</v>
+        <v>98.3</v>
       </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
-        <v>92.09999999999999</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4226,13 +4220,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
-        <v>97.40000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4288,19 +4282,19 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>97.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4356,19 +4350,19 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S18">
         <v>96.90000000000001</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4430,13 +4424,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>94.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4498,13 +4492,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>94.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4560,19 +4554,19 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S21">
         <v>92.2</v>
       </c>
       <c r="T21">
-        <v>97.3</v>
+        <v>98.3</v>
       </c>
       <c r="U21">
         <v>100</v>
       </c>
       <c r="V21">
-        <v>92.09999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4628,19 +4622,19 @@
         <v>87.5</v>
       </c>
       <c r="R22">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="S22">
         <v>92.2</v>
       </c>
       <c r="T22">
-        <v>91.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="U22">
         <v>100</v>
       </c>
       <c r="V22">
-        <v>86.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4696,19 +4690,19 @@
         <v>87.5</v>
       </c>
       <c r="R23">
-        <v>81.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S23">
         <v>92.2</v>
       </c>
       <c r="T23">
-        <v>86.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U23">
         <v>100</v>
       </c>
       <c r="V23">
-        <v>81.59999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4764,19 +4758,19 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S24">
         <v>98.40000000000001</v>
       </c>
       <c r="T24">
-        <v>97.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4832,19 +4826,19 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="S25">
         <v>100</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4900,19 +4894,19 @@
         <v>88.8</v>
       </c>
       <c r="R26">
-        <v>89.5</v>
+        <v>91.5</v>
       </c>
       <c r="S26">
         <v>98.40000000000001</v>
       </c>
       <c r="T26">
-        <v>89.2</v>
+        <v>91.5</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>86.8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4968,19 +4962,19 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="S27">
         <v>96.90000000000001</v>
       </c>
       <c r="T27">
-        <v>94.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="U27">
         <v>100</v>
       </c>
       <c r="V27">
-        <v>94.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5036,19 +5030,19 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S28">
         <v>98.40000000000001</v>
       </c>
       <c r="T28">
-        <v>97.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="U28">
         <v>100</v>
       </c>
       <c r="V28">
-        <v>97.40000000000001</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5110,13 +5104,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="U29">
         <v>100</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5172,7 +5166,7 @@
         <v>93.8</v>
       </c>
       <c r="R30">
-        <v>97.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S30">
         <v>95.3</v>
@@ -5184,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>94.7</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5240,19 +5234,19 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S31">
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
   </sheetData>
@@ -5309,7 +5303,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5318,19 +5312,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5341,7 +5335,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5350,19 +5344,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5376,25 +5370,25 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5408,25 +5402,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5572,7 +5566,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5613,13 +5607,13 @@
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5636,13 +5630,13 @@
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5659,13 +5653,13 @@
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5682,13 +5676,13 @@
         <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5702,16 +5696,16 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5719,47 +5713,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920078</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920012</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -799,25 +799,25 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -888,22 +888,22 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -977,25 +977,25 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1069,22 +1069,22 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1155,25 +1155,25 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1244,25 +1244,25 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1336,7 +1336,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1422,25 +1422,25 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1511,25 +1511,25 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1603,22 +1603,22 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1689,25 +1689,25 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1778,25 +1778,25 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1867,25 +1867,25 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1956,25 +1956,25 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2045,25 +2045,25 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2134,25 +2134,25 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2223,25 +2223,25 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2312,25 +2312,25 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2404,22 +2404,22 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2493,22 +2493,22 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2579,25 +2579,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2668,25 +2668,25 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2757,25 +2757,25 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2846,25 +2846,25 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2935,25 +2935,25 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3024,25 +3024,25 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3113,25 +3113,25 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3202,25 +3202,25 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5324,7 +5324,7 @@
         <v>17.9</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5356,7 +5356,7 @@
         <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>7.1</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5484,7 +5484,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/5AEV - Estadisticos 20231.xlsx
+++ b/grupos/5AEV - Estadisticos 20231.xlsx
@@ -799,25 +799,25 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -888,22 +888,22 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -977,25 +977,25 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1069,22 +1069,22 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1155,25 +1155,25 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1244,25 +1244,25 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1336,7 +1336,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1422,25 +1422,25 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1511,25 +1511,25 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1603,22 +1603,22 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1689,25 +1689,25 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1778,25 +1778,25 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1867,25 +1867,25 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1956,25 +1956,25 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2045,25 +2045,25 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2134,25 +2134,25 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2223,25 +2223,25 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2312,25 +2312,25 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2404,22 +2404,22 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2493,22 +2493,22 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2579,25 +2579,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2668,25 +2668,25 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2757,25 +2757,25 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2846,25 +2846,25 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2935,25 +2935,25 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3024,25 +3024,25 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3113,25 +3113,25 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3202,25 +3202,25 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5324,7 +5324,7 @@
         <v>17.9</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5356,7 +5356,7 @@
         <v>14.3</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5388,7 +5388,7 @@
         <v>7.1</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>3.6</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5484,7 +5484,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
